--- a/artfynd/A 43057-2022 artfynd.xlsx
+++ b/artfynd/A 43057-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43057-2022 artfynd.xlsx
+++ b/artfynd/A 43057-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,220 +1141,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112606531</v>
-      </c>
-      <c r="B6" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Koutojärvi, Nb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>882458</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7354776</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Övertorneå</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Hietaniemi</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112606533</v>
-      </c>
-      <c r="B7" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Koutojärvi, Nb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>882455</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7354879</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Övertorneå</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Hietaniemi</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43057-2022 artfynd.xlsx
+++ b/artfynd/A 43057-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104159853</v>
+        <v>104157997</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>882457.966903772</v>
+        <v>882546</v>
       </c>
       <c r="R2" t="n">
-        <v>7354775.511693497</v>
+        <v>7354763</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104157997</v>
+        <v>112606533</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>882547.1375652151</v>
+        <v>882455</v>
       </c>
       <c r="R3" t="n">
-        <v>7354763.439892443</v>
+        <v>7354879</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,27 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104159855</v>
+        <v>104157996</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>882454.5154737071</v>
+        <v>882536</v>
       </c>
       <c r="R4" t="n">
-        <v>7354879.29774098</v>
+        <v>7354760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104157996</v>
+        <v>112606531</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>882536.0608744018</v>
+        <v>882458</v>
       </c>
       <c r="R5" t="n">
-        <v>7354760.289129049</v>
+        <v>7354775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,27 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-08-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-29</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,6 +1080,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112606532</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Koutojärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>882514</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7354726</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43057-2022 artfynd.xlsx
+++ b/artfynd/A 43057-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157997</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606533</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104157996</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606531</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112606532</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>